--- a/AAII_Financials/Yearly/UNM_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/UNM_YR_FIN.xlsx
@@ -2471,10 +2471,10 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>34726900</v>
+        <v>34709100</v>
       </c>
       <c r="E47" s="3">
-        <v>37321200</v>
+        <v>37309700</v>
       </c>
       <c r="F47" s="3">
         <v>38410300</v>
@@ -2726,10 +2726,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2270100</v>
+        <v>2287900</v>
       </c>
       <c r="E52" s="3">
-        <v>1538700</v>
+        <v>1550200</v>
       </c>
       <c r="F52" s="3">
         <v>1565000</v>
